--- a/MVC.xlsx
+++ b/MVC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saikoro0615\プログラミング\家計簿_練習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saikoro0615\プログラミング\household_account\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79156B15-8C0B-41E8-B33C-9D1322D7371D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB32827-29ED-4FBE-95A5-BD7E25CD0C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{C77F9D69-FD8B-46B5-8E19-BD062EEB1628}"/>
   </bookViews>
@@ -105,20 +105,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>income(収入) or expence(支出)</t>
-    <rPh sb="7" eb="9">
-      <t>シュウニュウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>シシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>transcation</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -195,10 +181,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>5:expence_button</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>6:category_list</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -212,18 +194,6 @@
   </si>
   <si>
     <t>9:total_income_label</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>10:total_expence_label</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>11:total_income_and_expence_label</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>12:income_and_expence_list</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -249,6 +219,36 @@
     <rPh sb="7" eb="9">
       <t>イドウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>income(収入) or expense(支出)</t>
+    <rPh sb="7" eb="9">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5:expense_button</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:total_expense_label</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11:total_income_and_expense_label</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12:income_and_expense_list</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>transactions</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1922,7 +1922,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.55000000000000004">
@@ -1932,7 +1932,7 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.55000000000000004">
@@ -1959,46 +1959,46 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2014,62 +2014,62 @@
   <sheetData>
     <row r="18" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2089,10 +2089,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
